--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132551505</v>
       </c>
       <c r="B2" t="n">
-        <v>58631</v>
+        <v>58632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>132554432</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>132552549</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>132550622</v>
       </c>
       <c r="B5" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>132551396</v>
       </c>
       <c r="B6" t="n">
-        <v>58080</v>
+        <v>58081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132550949</v>
+        <v>132552902</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564873</v>
+        <v>564920</v>
       </c>
       <c r="R7" t="n">
-        <v>6433565</v>
+        <v>6433465</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även trumning</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132553848</v>
+        <v>132550949</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1425,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564857</v>
+        <v>564873</v>
       </c>
       <c r="R8" t="n">
-        <v>6433576</v>
+        <v>6433565</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Även trumning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132552902</v>
+        <v>132553848</v>
       </c>
       <c r="B9" t="n">
-        <v>57961</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564920</v>
+        <v>564857</v>
       </c>
       <c r="R9" t="n">
-        <v>6433465</v>
+        <v>6433576</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132551505</v>
       </c>
       <c r="B2" t="n">
-        <v>58632</v>
+        <v>58636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>132554432</v>
       </c>
       <c r="B3" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>132552549</v>
       </c>
       <c r="B4" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>132550622</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>132551396</v>
       </c>
       <c r="B6" t="n">
-        <v>58081</v>
+        <v>58085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>132552902</v>
       </c>
       <c r="B7" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>132550949</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>132553848</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132552902</v>
+        <v>132550949</v>
       </c>
       <c r="B7" t="n">
-        <v>57966</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564920</v>
+        <v>564873</v>
       </c>
       <c r="R7" t="n">
-        <v>6433465</v>
+        <v>6433565</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Även trumning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132550949</v>
+        <v>132553848</v>
       </c>
       <c r="B8" t="n">
         <v>57950</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1420,13 +1425,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564873</v>
+        <v>564857</v>
       </c>
       <c r="R8" t="n">
-        <v>6433565</v>
+        <v>6433576</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även trumning</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132553848</v>
+        <v>132552902</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564857</v>
+        <v>564920</v>
       </c>
       <c r="R9" t="n">
-        <v>6433576</v>
+        <v>6433465</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132551505</v>
       </c>
       <c r="B2" t="n">
-        <v>58636</v>
+        <v>58637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>132554432</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>132552549</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>132550622</v>
       </c>
       <c r="B5" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>132551396</v>
       </c>
       <c r="B6" t="n">
-        <v>58085</v>
+        <v>58086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132550949</v>
+        <v>132552902</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564873</v>
+        <v>564920</v>
       </c>
       <c r="R7" t="n">
-        <v>6433565</v>
+        <v>6433465</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även trumning</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132553848</v>
+        <v>132550949</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1425,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564857</v>
+        <v>564873</v>
       </c>
       <c r="R8" t="n">
-        <v>6433576</v>
+        <v>6433565</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Även trumning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132552902</v>
+        <v>132553848</v>
       </c>
       <c r="B9" t="n">
-        <v>57966</v>
+        <v>57951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564920</v>
+        <v>564857</v>
       </c>
       <c r="R9" t="n">
-        <v>6433465</v>
+        <v>6433576</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132552902</v>
+        <v>132553848</v>
       </c>
       <c r="B7" t="n">
-        <v>57967</v>
+        <v>57951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564920</v>
+        <v>564857</v>
       </c>
       <c r="R7" t="n">
-        <v>6433465</v>
+        <v>6433576</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132550949</v>
+        <v>132552902</v>
       </c>
       <c r="B8" t="n">
-        <v>57951</v>
+        <v>57967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564873</v>
+        <v>564920</v>
       </c>
       <c r="R8" t="n">
-        <v>6433565</v>
+        <v>6433465</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även trumning</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132553848</v>
+        <v>132550949</v>
       </c>
       <c r="B9" t="n">
         <v>57951</v>
@@ -1532,7 +1527,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564857</v>
+        <v>564873</v>
       </c>
       <c r="R9" t="n">
-        <v>6433576</v>
+        <v>6433565</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1581,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även trumning</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132553848</v>
+        <v>132552902</v>
       </c>
       <c r="B7" t="n">
-        <v>57951</v>
+        <v>57967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564857</v>
+        <v>564920</v>
       </c>
       <c r="R7" t="n">
-        <v>6433576</v>
+        <v>6433465</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132552902</v>
+        <v>132550949</v>
       </c>
       <c r="B8" t="n">
-        <v>57967</v>
+        <v>57951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564920</v>
+        <v>564873</v>
       </c>
       <c r="R8" t="n">
-        <v>6433465</v>
+        <v>6433565</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Även trumning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132550949</v>
+        <v>132553848</v>
       </c>
       <c r="B9" t="n">
         <v>57951</v>
@@ -1527,7 +1532,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1536,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564873</v>
+        <v>564857</v>
       </c>
       <c r="R9" t="n">
-        <v>6433565</v>
+        <v>6433576</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,12 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även trumning</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132552902</v>
+        <v>132553848</v>
       </c>
       <c r="B7" t="n">
-        <v>57971</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564920</v>
+        <v>564857</v>
       </c>
       <c r="R7" t="n">
-        <v>6433465</v>
+        <v>6433576</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132550949</v>
+        <v>132552902</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>57971</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564873</v>
+        <v>564920</v>
       </c>
       <c r="R8" t="n">
-        <v>6433565</v>
+        <v>6433465</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även trumning</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132553848</v>
+        <v>132550949</v>
       </c>
       <c r="B9" t="n">
         <v>57955</v>
@@ -1532,7 +1527,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564857</v>
+        <v>564873</v>
       </c>
       <c r="R9" t="n">
-        <v>6433576</v>
+        <v>6433565</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1581,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även trumning</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15162-2026 artfynd.xlsx
+++ b/artfynd/A 15162-2026 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132551505</v>
+        <v>132550622</v>
       </c>
       <c r="B2" t="n">
-        <v>58641</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564897</v>
+        <v>564862</v>
       </c>
       <c r="R2" t="n">
-        <v>6433530</v>
+        <v>6433548</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På flera torrakor i området. Födosök, sång/läte och trumning. Även observerad visuellt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132554432</v>
+        <v>132552902</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,7 +831,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564860</v>
+        <v>564920</v>
       </c>
       <c r="R3" t="n">
-        <v>6433579</v>
+        <v>6433465</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,14 +912,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132552549</v>
+        <v>132550949</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,7 +947,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564965</v>
+        <v>564873</v>
       </c>
       <c r="R4" t="n">
-        <v>6433429</v>
+        <v>6433565</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även trumning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,27 +1033,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132550622</v>
+        <v>132552549</v>
       </c>
       <c r="B5" t="n">
-        <v>57971</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1058,7 +1068,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1067,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564862</v>
+        <v>564965</v>
       </c>
       <c r="R5" t="n">
-        <v>6433548</v>
+        <v>6433429</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,12 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera torrakor i området. Födosök, sång/läte och trumning. Även observerad visuellt.</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,32 +1149,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132551396</v>
+        <v>132553848</v>
       </c>
       <c r="B6" t="n">
-        <v>58090</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205976</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1179,7 +1184,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,13 +1193,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564897</v>
+        <v>564857</v>
       </c>
       <c r="R6" t="n">
-        <v>6433540</v>
+        <v>6433576</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,14 +1265,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132553848</v>
+        <v>132554432</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1304,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564857</v>
+        <v>564860</v>
       </c>
       <c r="R7" t="n">
-        <v>6433576</v>
+        <v>6433579</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,27 +1381,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132552902</v>
+        <v>132551505</v>
       </c>
       <c r="B8" t="n">
-        <v>57971</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,7 +1411,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1420,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564920</v>
+        <v>564897</v>
       </c>
       <c r="R8" t="n">
-        <v>6433465</v>
+        <v>6433530</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,32 +1497,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132550949</v>
+        <v>132551396</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>58107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>205976</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1536,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564873</v>
+        <v>564897</v>
       </c>
       <c r="R9" t="n">
-        <v>6433565</v>
+        <v>6433540</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,12 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även trumning</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
